--- a/file/테크윙.xlsx
+++ b/file/테크윙.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\0. JupyterNotebook\Finance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\0. JupyterNotebook\Finance\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B564E919-0BEE-49A5-A022-18663F561BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D0A632-ECD7-47FB-B2D8-1EF4B1CF3BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{C05637EF-894A-4FAC-9F47-0179780C4CC4}"/>
   </bookViews>
@@ -1206,7 +1206,7 @@
         <v>800</v>
       </c>
       <c r="F2" s="3">
-        <f>E2*100000000/B2*35</f>
+        <f>MAX(E2*100000000/B2*35, 0)</f>
         <v>74959.217500728511</v>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
         <v>700</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F27" si="0">E3*100000000/B3*35</f>
+        <f t="shared" ref="F3:F27" si="0">MAX(E3*100000000/B3*35, 0)</f>
         <v>65589.315313137442</v>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F6" s="3">
         <f t="shared" si="0"/>
-        <v>-1967.6794593941233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F9" s="3">
         <f t="shared" si="0"/>
-        <v>-7402.2227281969408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F10" s="3">
         <f t="shared" si="0"/>
-        <v>-37760.705815991991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="F13" s="3">
         <f t="shared" si="0"/>
-        <v>-8526.610990707868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="F14" s="3">
         <f t="shared" si="0"/>
-        <v>-2248.7765250218554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F15" s="3">
         <f t="shared" si="0"/>
-        <v>-14523.348390766148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F16" s="3">
         <f t="shared" si="0"/>
-        <v>-19489.396550189413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6">
